--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:20</t>
+    <t xml:space="preserve">2026-09-09 22:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:19</t>
+    <t xml:space="preserve">2026-09-17 13:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1243,18 +1243,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3.7</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4.48</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="4">
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>4.17</v>
+        <v>4.48</v>
       </c>
     </row>
   </sheetData>
@@ -1327,101 +1327,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>7.48</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5.06</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>7.09</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5.16</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3.7</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4.58</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>6</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4.48</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5.26</v>
+        <v>4.58</v>
       </c>
     </row>
     <row r="11">
@@ -1558,35 +1558,35 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5.45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>4.17</v>
+        <v>4.48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>5.02</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="26">

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:45</t>
+    <t xml:space="preserve">2026-09-25 21:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -565,7 +565,7 @@
         <v>-1.3</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-31.25</v>
+        <v>-31.19</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>9</v>
@@ -588,7 +588,7 @@
         <v>-1.46</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-28.29</v>
+        <v>-28.21</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>9</v>
@@ -611,7 +611,7 @@
         <v>-1.49</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-22.21</v>
+        <v>-22.26</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>8</v>
@@ -634,7 +634,7 @@
         <v>-1.13</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-25.39</v>
+        <v>-25.47</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>8</v>
@@ -657,7 +657,7 @@
         <v>-1.28</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-23.49</v>
+        <v>-23.56</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>8</v>
@@ -680,7 +680,7 @@
         <v>-2.01</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-27.57</v>
+        <v>-27.62</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>7</v>
@@ -703,7 +703,7 @@
         <v>-1.8</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-33.03</v>
+        <v>-33</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>7</v>
@@ -726,7 +726,7 @@
         <v>-1.88</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-30.32</v>
+        <v>-30.34</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>7</v>
@@ -749,7 +749,7 @@
         <v>-1.65</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-23.64</v>
+        <v>-23.58</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>6</v>
@@ -769,10 +769,10 @@
         <v>5.07</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-1.43</v>
+        <v>-1.44</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-28.21</v>
+        <v>-28.34</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>6</v>
@@ -795,7 +795,7 @@
         <v>-1.52</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-25.81</v>
+        <v>-25.82</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>6</v>
@@ -818,7 +818,7 @@
         <v>-1.74</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-23.67</v>
+        <v>-23.68</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>5</v>
@@ -841,7 +841,7 @@
         <v>-1.39</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-27.36</v>
+        <v>-27.37</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>5</v>
@@ -864,7 +864,7 @@
         <v>-1.53</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-25.5</v>
+        <v>-25.46</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>5</v>
@@ -907,10 +907,10 @@
         <v>5.41</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-1.55</v>
+        <v>-1.54</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-28.65</v>
+        <v>-28.54</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>4</v>
@@ -930,10 +930,10 @@
         <v>6</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-1.52</v>
+        <v>-1.51</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-25.33</v>
+        <v>-25.21</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>4</v>
@@ -956,7 +956,7 @@
         <v>-2.28</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-32.29</v>
+        <v>-32.28</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>3</v>
@@ -976,10 +976,10 @@
         <v>7.95</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-2.61</v>
+        <v>-2.6</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-32.83</v>
+        <v>-32.77</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>3</v>
@@ -999,10 +999,10 @@
         <v>7.48</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-2.42</v>
+        <v>-2.43</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-32.35</v>
+        <v>-32.42</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>3</v>
@@ -1022,10 +1022,10 @@
         <v>7.88</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>-2.12</v>
+        <v>-2.13</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-26.9</v>
+        <v>-26.96</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>2</v>
@@ -1048,7 +1048,7 @@
         <v>-2.08</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-31.18</v>
+        <v>-31.24</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>2</v>
@@ -1071,7 +1071,7 @@
         <v>-2.1</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-29.21</v>
+        <v>-29.18</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>2</v>
@@ -1094,7 +1094,7 @@
         <v>-1.9</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-24.08</v>
+        <v>-24.1</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>1</v>
@@ -1117,7 +1117,7 @@
         <v>-2.08</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-31.56</v>
+        <v>-31.52</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>1</v>
@@ -1140,7 +1140,7 @@
         <v>-2</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-28.05</v>
+        <v>-28.03</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>1</v>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_valparaiso.xlsx
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:41</t>
+    <t xml:space="preserve">2026-10-05 07:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
